--- a/public/templates/template_import_barang.xlsx
+++ b/public/templates/template_import_barang.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Template Import" sheetId="1" r:id="rId4"/>
-    <sheet name="Instruksi" sheetId="2" r:id="rId5"/>
+    <sheet name="Data Cabang" sheetId="2" r:id="rId5"/>
+    <sheet name="Instruksi" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -16,11 +17,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
   <si>
     <t>Nama Barang</t>
   </si>
   <si>
+    <t>Cabang</t>
+  </si>
+  <si>
     <t>Satuan</t>
   </si>
   <si>
@@ -30,21 +34,42 @@
     <t>Pulpen Snowman</t>
   </si>
   <si>
+    <t>Gudang Pusat</t>
+  </si>
+  <si>
     <t>Box</t>
   </si>
   <si>
     <t>Kertas HVS A4</t>
   </si>
   <si>
+    <t>Bandung</t>
+  </si>
+  <si>
     <t>Rim</t>
   </si>
   <si>
     <t>Mouse Logitech</t>
   </si>
   <si>
+    <t>Jakarta Pusat</t>
+  </si>
+  <si>
     <t>Pcs</t>
   </si>
   <si>
+    <t>Daftar Cabang Terdaftar</t>
+  </si>
+  <si>
+    <t>Jakarta Timur</t>
+  </si>
+  <si>
+    <t>Medan</t>
+  </si>
+  <si>
+    <t>Surabaya</t>
+  </si>
+  <si>
     <t>INSTRUKSI PENGGUNAAN TEMPLATE IMPORT BARANG</t>
   </si>
   <si>
@@ -55,6 +80,9 @@
   </si>
   <si>
     <t xml:space="preserve">   - Nama Barang: Nama barang (wajib diisi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Cabang: Nama cabang (Lihat referensi di sheet "Data Cabang")</t>
   </si>
   <si>
     <t xml:space="preserve">   - Satuan: Pilih salah satu (Pcs, Box, Rim, Pack, Unit)</t>
@@ -168,12 +196,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -474,15 +503,17 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
-    <col min="2" max="2" width="15" customWidth="true" style="0"/>
+    <col min="2" max="2" width="20" customWidth="true" style="0"/>
     <col min="3" max="3" width="15" customWidth="true" style="0"/>
+    <col min="4" max="4" width="15" customWidth="true" style="0"/>
+    <col min="6" max="6" width="25" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" customHeight="1" ht="25">
+    <row r="1" spans="1:6" customHeight="1" ht="25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,37 +523,50 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2">
         <v>25</v>
       </c>
     </row>
@@ -547,55 +591,122 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="80" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="3" t="s">
-        <v>9</v>
+      <c r="A1" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
